--- a/Buffers.xlsx
+++ b/Buffers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ABAP 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59DE13F-9BBC-49A7-8C15-57237A473707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8DFF80F-69BC-427D-976D-78F4F9D94ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="6876" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>Full Record Buffering</t>
   </si>
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>*&amp;---------------------------------------------------------------------*</t>
-  </si>
-  <si>
-    <t>REPORT zprg_single_buffer_sr.</t>
   </si>
   <si>
     <t>*------------------- TYPES DECLARATION -------------------*</t>
@@ -614,7 +611,7 @@
   <sheetData>
     <row r="6" spans="2:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
@@ -646,7 +643,7 @@
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.3">
@@ -654,62 +651,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
@@ -717,17 +709,17 @@
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.3">
@@ -735,12 +727,12 @@
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.3">
@@ -748,57 +740,57 @@
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.3">
@@ -806,22 +798,22 @@
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.3">
@@ -829,52 +821,52 @@
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.3">
@@ -882,7 +874,7 @@
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
